--- a/WIFI_Financial_Statements.xlsx
+++ b/WIFI_Financial_Statements.xlsx
@@ -404,6 +404,21 @@
         <t>2024 sub-line values extracted from 2024 AR p.245. Note 5 = Net 136,493,664,425 matches Balance Sheet. Three additional 2024 customers appended below.</t>
       </text>
     </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.245: 'PT Jaring Logstik Indonesia -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.245: 'PT Phatria Inti Persada -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.245: 'nilai' (keyword)</t>
+      </text>
+    </comment>
     <comment ref="C62" authorId="0" shapeId="0">
       <text>
         <t>Item not in 2025 report</t>
@@ -417,6 +432,71 @@
     <comment ref="C64" authorId="0" shapeId="0">
       <text>
         <t>Item not in 2025 report</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Laksana Bumi Hjau - 8.325.845.824 PT Laksana Bumi Hjau"</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Lini Imaji Kreasi Ekosistem Tbk - 4.966.400.000 Ekosistem Tbk"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT XL Axiata Tbk - 2.377.279.869 PT XL Axiata Tbk"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Eka Mas Republik - 523.022.750 PT Eka Mas Republik"</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Berlian Promosindo - 418.650.000 PT Berlian Promosindo"</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Wira Pamungkas Pariwara - 316.350.000 PT Wira Pamungkas Pariwara"</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Power Telecom - 371.850.000 PT Power Telecom"</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Moving Walls Indonesia - 299.145.000 PT Moving Walls Indonesia"</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Wifian Solution - 206.262.420 PT Wifian Solution"</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Pharos Indonesia - 154.000.000 PT Pharos Indonesia"</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "Perusahaan Umum Damri - 138.901.875 Perusahaan Umum Damri"</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Budaya Anak Negeri - 112.800.000 PT Budaya Anak Negeri"</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.245. Line: "PT Kreasi Bilangan Sempurna - 104.895.000 PT Kreasi Bilangan Sempurna"</t>
       </text>
     </comment>
   </commentList>
@@ -514,6 +594,56 @@
         <t>Not found in 2024 report</t>
       </text>
     </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "PT Cahaya Surya Kemilau 161.854.400.000 - PT Cahaya Surya Kemilau"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "PT Eka Jaya Maxima 72.360.000.000 - PT Eka Jaya Maxima"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "PT Ads Plafrom Indonesia 5.800.000.000 3.500.000.000 PT Ads Plafrom Indonesia"</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "PT Pulau Pulau Media 1.081.999.979 1.081.999.979 PT Pulau Pulau Media"</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "Pengurusan izin 1.747.053.519 1.088.124.921 Licensing of network"</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "Biaya operasional 500.000.000 462.437.600 Operating cost"</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "Uang muka pembelian aset tetap - 88.384.436.054 Advance purchase of fixed assets"</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "T otal 393.686.379.659 133.061.369.540 Total"</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "jasa pembangunan FTTH sebesar Rp 120.000.000.000 to Rp 120,000,000,000 in accordance with agreement"</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.247. Line: "uang muka untuk biaya sewa tersebut sebesar the rental fee was Rp 72,360,000,000 in accordance"</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -544,6 +674,76 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.248 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Tanah' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Bangunan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Kendaraan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Peralatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'dan perabotan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Project equipments' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Project equipments' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Bangunan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Kendaraan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Peralatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'perabotan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Project equipments' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Total' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.248: 'Nilai Buku Neto' (substring)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -559,6 +759,26 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.251 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.251: 'Captive Portal Software' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.251: 'Perangkat lunak - - -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.251: 'Captive Portal Software' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.251: 'Nila i Buku Neto' (substring)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -601,107 +821,197 @@
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
+        <t>Matched from PDF p.252: 'Indonesia -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0">
+    <comment ref="B23" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B23" authorId="0" shapeId="0">
+    <comment ref="B24" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0">
+    <comment ref="B25" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0">
+    <comment ref="B26" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="0" shapeId="0">
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'PT Era Media Sejahtera -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: '(KOPINDOSAT)' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'PT Cahaya Agung Oetama' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'PT Kereta Api Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'PT Laksana Bumi Berseri' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'PT Cahaya Surya Kemilau' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'PT Knet Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Sub-total / Total Trade Payables 2024 (matches BS)</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>Total trade payables 2024</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'Belum jatuh tempo' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'days' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'days' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'Lebih dari' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B27" authorId="0" shapeId="0">
+    <comment ref="B46" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B30" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B31" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B32" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B33" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B34" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B37" authorId="0" shapeId="0">
-      <text>
-        <t>Sub-total / Total Trade Payables 2024 (matches BS)</t>
-      </text>
-    </comment>
-    <comment ref="B38" authorId="0" shapeId="0">
-      <text>
-        <t>Total trade payables 2024</t>
-      </text>
-    </comment>
-    <comment ref="B40" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B42" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B43" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B44" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B45" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B46" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Solidsteel Tamajaya Indonesia 915.147.270 - PT Solidsteel Tamajaya Indonesia"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "Shinta Sriwijaya &amp; Co 855.000.000 60.000.000 Shinta Sriwijaya &amp; Co"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Winnow Wastu Wilasa 661.560.000 661.560.000 PT Winnow Wastu Wilasa"</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Paramitha Adikarya Tekno 610.197.416 - PT Paramitha Adikarya Tekno"</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Nunut Eldana Prima 580.362.256 - PT Nunut Eldana Prima"</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Sompo Insurance 421.740.410 1.346.439.365 PT Sompo Insurance"</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Aquila Wijaya Teknik 404.270.412 438.194.812 PT Aquila Wijaya Teknik"</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Kalibesar Raya Utama 372.472.890 154.594.386 PT Kalibesar Raya Utama"</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Bisnis Ini Sinergi 113.217.786 - PT Bisnis Ini Sinergi"</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Ilab Komunikasi Indonesia - 60.713.000 PT Ilab Komunikasi Indonesia"</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Lini Imaji Kreasi Ekosistem Tbk - 2.865.976.000 PT Lini Imaji Kreasi Ekosistem Tbk"</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT IP Network Solusindo - 1.908.081.619 PT IP Network Solusindo"</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Pradikta Unggul - 842.094.955 PT Pradikta Unggul"</t>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Davon Media Teknologi - 561.577.121 PT Davon Media Teknologi"</t>
+      </text>
+    </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Multipolar Technology - 532.519.070 PT Multipolar Technology"</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "CV Infra Media Solusindo - 359.069.650 CV Infra Media Solusindo"</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Telekomindo Global Mandiri - 304.362.000 PT Telekomindo Global Mandiri"</t>
+      </text>
+    </comment>
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "PT Sepur Berkah Komunikasi - 164.596.500 PT Sepur Berkah Komunikasi"</t>
       </text>
     </comment>
   </commentList>
@@ -719,6 +1029,11 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.252 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.252: 'PT Investasi Gemilang Maju' (keyword)</t>
+      </text>
+    </comment>
     <comment ref="B51" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report — related parties under accrued/other current items</t>
@@ -741,22 +1056,22 @@
     </comment>
     <comment ref="B56" authorId="0" shapeId="0">
       <text>
+        <t>Matched from PDF p.252: 'PT Prambanan Investasi Sukses' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
     <comment ref="B58" authorId="0" shapeId="0">
       <text>
-        <t>Not found in 2024 report</t>
+        <t>Matched from PDF p.252: 'Beban bunga (Catatan' (substring)</t>
       </text>
     </comment>
     <comment ref="B59" authorId="0" shapeId="0">
       <text>
-        <t>Not found in 2024 report</t>
+        <t>Matched from PDF p.252: 'Pajak penghasilan atas bunga' (substring)</t>
       </text>
     </comment>
     <comment ref="B60" authorId="0" shapeId="0">
@@ -767,6 +1082,11 @@
     <comment ref="B63" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report — Day-one profit on related-party borrowings appears 2025</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.252. Line: "S ubtotal 301.212.468.808 - Subtotal"</t>
       </text>
     </comment>
   </commentList>
@@ -806,32 +1126,37 @@
     </comment>
     <comment ref="B53" authorId="0" shapeId="0">
       <text>
+        <t>Matched from PDF p.254: 'R etribusi' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B54" authorId="0" shapeId="0">
+    <comment ref="B55" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B55" authorId="0" shapeId="0">
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.254: 'Jasa profesional' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <t>Not found in 2024 report</t>
       </text>
     </comment>
-    <comment ref="B56" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
-      <text>
-        <t>Not found in 2024 report</t>
-      </text>
-    </comment>
     <comment ref="B58" authorId="0" shapeId="0">
       <text>
         <t>Total Accrued Expenses 2024 (matches BS)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.254. Line: "Utilitas 33.517.500 - Utilitas"</t>
       </text>
     </comment>
   </commentList>
@@ -899,6 +1224,11 @@
         <t>Long-term portion 2024 (matches BS row 52)</t>
       </text>
     </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.255: 'B agian jangka panjang' (substring)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -914,6 +1244,11 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.255 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.255: 'B agian jangka panjang' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
         <t>Utang angsuran 2024</t>
@@ -942,6 +1277,21 @@
     <comment ref="B53" authorId="0" shapeId="0">
       <text>
         <t>Long-term portion 2024 (matches BS row 54)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.255. Line: "Gedung kantor 2.492.608.193 (1.147.431.524 ) 1.345.176.669 Office building"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.255. Line: "Dark fiber 5.939.208.780 (3.666.666.667 ) 2.272.542.113 Dark fiber"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.255. Line: "Tanah 268.509.380.095 (73.947.901.271 ) 194.561.478.824 Land"</t>
       </text>
     </comment>
   </commentList>
@@ -974,6 +1324,106 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.257 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.257: 'Pajak Pertambahan Nilai -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.257: 'Pajak Pertambahan Nilai' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>Total Pajak Dibayar di Muka 2024 (matches BS row 11)</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.257: 'Pajak Pertambahan Nilai' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>Sub-total Perusahaan Utang Pajak 2024</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.257: 'Pajak Pertambahan Nilai' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.257: 'Pajak Final' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Sub-total Entitas Anak Utang Pajak 2024</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Total Utang Pajak 2024 (matches BS row 36)</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Pajak kini - Perusahaan 2024 (sign flipped per IS expense convention)</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>Pajak kini - Entitas Anak 2024 (sign flipped per IS expense convention)</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>Total Pajak Kini 2024 (sign flipped per IS expense convention)</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Pajak tangguhan - Perusahaan 2024</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>Pajak tangguhan - Entitas Anak 2024 (net benefit)</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>Total Pajak Tangguhan 2024 (net benefit)</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>Beban pajak penghasilan - net 2024 (matches IS row 17)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.257. Line: "Perusahaan 13.049.014.880 679.452.400 The Company"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.257. Line: "Entitas Anak 25.237.579.300 4.035.370.020 Subsidiaries"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.257. Line: "Total pajak kini 38.286.594.180 4.714.822.420 Total current tax"</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.257. Line: "penghasilan - neto 43.102.216.446 9.318.897.299 expense - net"</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -989,6 +1439,16 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.261 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.261: 'PT BCA Finance' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
+      <text>
+        <t>Current portion 2024 (matches BS row 41)</t>
+      </text>
+    </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t>Less: current maturities 2024 (matches BS row 41)</t>
@@ -997,6 +1457,41 @@
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>Long-term portion 2024 (matches BS row 55)</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.261: 'Jumlah fasilitas pembiayaan : Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.261: 'Jumlah fasilitas pembiayaan : Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.261: 'Jumlah fasilitas pembiayaan : Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.261: 'Jumlah fasilitas pembiayaan : Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.261: 'Jumlah fasilitas pembiayaan : Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.261: 'Jumlah fasilitas pembiayaan : Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.261. Line: "Jumlah fasilitas pembiayaan : Rp 703.692.480 Total financing facility : Rp 703,692,480"</t>
       </text>
     </comment>
   </commentList>
@@ -1014,9 +1509,24 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.262 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.262: 'PT Bank Hibank Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.262: 'PT BPR Kirana Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Current portion 2024 (matches BS row 42)</t>
+      </text>
+    </comment>
     <comment ref="B47" authorId="0" shapeId="0">
       <text>
-        <t>Sub-total Bank Loans 2024 (=current 138,055,277,673 + long-term 237,250,226,847)</t>
+        <t>Sub-total LT bank loans 2024</t>
       </text>
     </comment>
     <comment ref="B49" authorId="0" shapeId="0">
@@ -1027,6 +1537,26 @@
     <comment ref="B50" authorId="0" shapeId="0">
       <text>
         <t>Long-term portion 2024 (matches BS row 56)</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.262: 'Plafond : Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.262. Line: "PT Bank J Trust Indonesia 149.875.000.004 126.250.000.000 PT Bank J Trust Indonesia"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.262. Line: "(Persero) Tbk - 212.476.592.826 (Persero) Tbk"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.262. Line: "diamortisasi (2.001.000.000 ) (1.880.000.000 ) expense amortized"</t>
       </text>
     </comment>
   </commentList>
@@ -1044,9 +1574,29 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.277 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.277: 'O bligasi Seri A' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.277: 'O bligasi Seri B' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.277: 'O bligasi Seri C' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.277: 'B unga obligasi' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B25" authorId="0" shapeId="0">
       <text>
-        <t>Sub-total Bonds Payable 2024 (=current 166,632,590,847 + long-term 447,452,484,087)</t>
+        <t>Sub-total Bonds 2024</t>
       </text>
     </comment>
     <comment ref="B27" authorId="0" shapeId="0">
@@ -1057,6 +1607,31 @@
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
         <t>Long-term portion 2024 (matches BS row 58)</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.277: 'sebesar Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.277: 'sebesar Rp' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.277. Line: "B iaya emisi obligasi (3.257.302.844 ) - Bond issuence cost"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.277. Line: "tahun 166.632.590.847 - maturities"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.277. Line: "masyarakat dengan nilai nominal sebesar a n o m i n a l v a l u e o f R p 600,000,000,000."</t>
       </text>
     </comment>
   </commentList>
@@ -1074,19 +1649,49 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.278 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.278: 'Finance Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.278: 'PT KDB Tifa Finance Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.278: 'PT Radana Bhasakara Finance Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.278: 'PT Akulaku Finance Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.278: 'PT Pegadaian (Persero)' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>Total Loans 2024 (=current 83,918,554,209 + long-term 34,204,122,692)</t>
+        <t>Total Loans 2024</t>
       </text>
     </comment>
     <comment ref="B47" authorId="0" shapeId="0">
       <text>
-        <t>Less: current maturities 2024 (matches BS row 43)</t>
+        <t>Current portion 2024 (matches BS row 43)</t>
       </text>
     </comment>
     <comment ref="B48" authorId="0" shapeId="0">
       <text>
         <t>Long-term portion 2024 (matches BS row 57)</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.278: 'Indonesia sebesar Rp' (substring)</t>
       </text>
     </comment>
   </commentList>
@@ -1104,9 +1709,29 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.281 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.281: 'Saldo awal' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.281: 'Penambahan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.281: 'Beban bunga (Catatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.281: 'Pajak penghasilan atas bunga' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B59" authorId="0" shapeId="0">
       <text>
-        <t>Sub-total Due to Related Parties (non-current) 2024 (matches BS row 50)</t>
+        <t>Total Due to Related Parties 2024 (matches BS row 50)</t>
       </text>
     </comment>
   </commentList>
@@ -1234,9 +1859,34 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.284 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.284: 'B iaya jasa kini' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.284: 'Biaya bunga' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B63" authorId="0" shapeId="0">
       <text>
         <t>Total Employee Benefits Liability 2024 (matches BS row 51)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.284. Line: "laba rugi (Catatan 27) 1.181.193.420 924.621.073 in profit or loss (Note 27)"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.284. Line: "komprehensif lain (538.204.957) 103.139.793 comprehensive income"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.284. Line: "T otal 642.988.463 1.027.760.866 Total"</t>
       </text>
     </comment>
   </commentList>
@@ -1254,6 +1904,11 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.285 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.285: 'kurang dari' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B48" authorId="0" shapeId="0">
       <text>
         <t>Number of issued shares 2024</t>
@@ -1262,6 +1917,11 @@
     <comment ref="B49" authorId="0" shapeId="0">
       <text>
         <t>Issued and paid-in capital 2024 (matches BS row 65)</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.285: 'PT Investasi Sukses Bersama' (substring)</t>
       </text>
     </comment>
   </commentList>
@@ -1279,9 +1939,29 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.286 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.286: '(Catatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.286: 'Pengampunan pajak' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B62" authorId="0" shapeId="0">
       <text>
-        <t>Total Additional Paid-in Capital 2024 (matches BS row 66)</t>
+        <t>Total APIC 2024 (matches BS row 66)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.286. Line: "PMTHMETD (Catatan 22) 17.632.494.000 17.632.494.000 PMTHMETD (Note 22)"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.286. Line: "Biaya emisi saham (Catatan 1c) (3.532.387.928 ) (3.532.387.928 ) Issuance costs of share (Note 1c)"</t>
       </text>
     </comment>
   </commentList>
@@ -1299,9 +1979,79 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.287 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Gawai Maju Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Jejaring Digital Utama' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'P T Kreasi Kode Digital' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Sinergi Apta Media' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Sinergi Aplikasi Akurat' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Media Digital Selaras' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Laper Nih Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Aspek Media Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Sinergi Media Digital' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Integrasi Media Terkini' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT Laju Inti Digital' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
         <t>Total NCI 2024 (matches BS)</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.287. Line: "PT Solusi Pariwisata Digital (140.794.054) (53.300.880 ) PT Solusi Pariwisata Digital"</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.287. Line: "PT Jaringan Infra Andalan (158.847.364) (95.794.715 ) PT Jaringan Infra Andalan"</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.287. Line: "PT Integrasi Jaringan Ekosistem - 2.180.891.352 PT Integrasi Jaringan Ekosistem"</t>
       </text>
     </comment>
   </commentList>
@@ -1319,9 +2069,69 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.287 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'Nusantara -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'Bandwidth' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'Sewa core' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'Colocation' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'I klan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'Potongan harga' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
         <t>Net Revenue 2024 (matches IS)</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'Investindo' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.287: 'PT XL Axiata Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.287. Line: "Manage telco service 25.079.825.000 - Manage telco service"</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.287. Line: "Portal web dan platform digital - 57.460.084.820 Web portal and digital platform"</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.287. Line: "Bersama - 0% 30.568.475.676 6,96% Bersama"</t>
       </text>
     </comment>
   </commentList>
@@ -1339,9 +2149,24 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.288 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'P eriklanan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Portal web dan platform digital' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
         <t>Total Cost of Revenues 2024 (matches |IS|)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Telekomunikasi 89.515.154.515 71.085.873.331 Telecommunication"</t>
       </text>
     </comment>
   </commentList>
@@ -1359,6 +2184,91 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.288 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Gaji, THR dan tunjangan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'pemasaran' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Beban pajak' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Penyusutan (Catatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Jasa profesional' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Transportasi dan perjalanan dinas' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Asuransi' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Administrasi efek' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'dan listrik' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Perlengkapan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Natura' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Alat tulis dan cetakan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Komisi - 78.014.659 Commission"</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Perizinan 10.157.803.693 5.195.403.818 License"</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Jamuan dan sumbangan 2.453.754.352 828.648.781 Entertain and donations"</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Sewa 1.642.856.856 4.317.860.976 Rent"</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Pemeliharaan dan perawatan 337.113.233 461.416.146 Maintenance and care"</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1374,9 +2284,29 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.288 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: '(Catatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'usaha (Catatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'Penghapusan piutang usaha -' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
         <t>Other income (expense) - net 2024 (matches IS row 11)</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Laba pelepasan entitas anak - 445.566.411 Profit on disposal of subsidiary entity"</t>
       </text>
     </comment>
   </commentList>
@@ -1394,9 +2324,19 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.288 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.288: 'dan jasa giro bank' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B33" authorId="0" shapeId="0">
       <text>
         <t>Finance income 2024 (matches IS row 14)</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.288. Line: "Penghasilan bunga kontraktrual - 162.456.900 Contractual interest income"</t>
       </text>
     </comment>
   </commentList>
@@ -1459,6 +2399,31 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.289 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: '(Catatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: 'Biaya administrasi bank' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: 'Bunga pinjaman (Catatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: 'Bunga pinjaman bank' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: 'Bunga obligasi' (substring)</t>
+      </text>
+    </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
         <t>Finance costs 2024 (matches IS row 15)</t>
@@ -1484,6 +2449,11 @@
         <t>NP attributable to parent 2024</t>
       </text>
     </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: 'Jumlah rata-rata saham tertimbang' (substring)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1499,6 +2469,31 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.289 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: 'PT Investasi Sukses Bersama' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.289: 'PT LHT Internasional' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.289. Line: "Saldo awal - 120.262.110.434 Beginning balance"</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.289. Line: "Pembayaran tahun berjalan - (120.400.198.799) Additional current year"</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.289. Line: "Pajak atas penghasilan bunga - (24.368.535) Tax of interest income"</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1544,6 +2539,46 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.293 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'Pendapatan neto' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'Beban pokok pendapatan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'Laba bruto' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'Beban usaha - neto' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'L aba usaha' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'Aset segmen' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'Liabilitas segmen' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.293: 'Penyusutan' (substring)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1559,6 +2594,81 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.294 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'hari ke-' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Beban bunga kontraktual - neto' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Pajak penghasilan' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Penambahan dari beban bunga' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Penambahan dari beban bunga' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Uang muka penjualan' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Pinjaman' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Liabilitas sewa' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'konsumen' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Utang bank' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Liabilitas sewa' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'panjang -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Utang pihak berelasi' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.294: 'Utang obligasi -' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.294. Line: "Pendapatan bunga kontraktual - 162.456.900 Contractual interest income"</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1589,6 +2699,11 @@
         <t>2024 column added. Detailed sub-line values from 2024 PDF p.325 available in source; main statement totals are populated in BS/IS/CF sheets.</t>
       </text>
     </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.325. Line: "invoice yang di biayai sebesar Rp 8.679.000.000 dan funded of Rp 8,679,000,000 and the value that can be"</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1614,6 +2729,31 @@
     <author>Append2024</author>
   </authors>
   <commentList>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Indonesian title: UMUM</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Indonesian title: INFORMASI KEBIJAKAN AKUNTANSI MATERIAL</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Indonesian title: ESTIMASI DAN PERTIMBANGAN AKUNTANSI YANG SIGNIFIKAN</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Indonesian title: KAS DAN SETARA KAS</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Indonesian title: PIUTANG USAHA</t>
+      </text>
+    </comment>
     <comment ref="B8" authorId="0" shapeId="0">
       <text>
         <t>Note not present in 2024 report</t>
@@ -1621,12 +2761,12 @@
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 6.</t>
+        <t>In 2024 this topic was Note 6. Indonesian title: BEBAN DIBAYAR DI MUKA DAN ASET LANCAR LAINNYA</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 7.</t>
+        <t>In 2024 this topic was Note 7. Indonesian title: UANG MUKA</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
@@ -1636,12 +2776,12 @@
     </comment>
     <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 8.</t>
+        <t>In 2024 this topic was Note 8. Indonesian title: ASET TETAP</t>
       </text>
     </comment>
     <comment ref="B13" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 9.</t>
+        <t>In 2024 this topic was Note 9. Indonesian title: ASET TAKBERWUJUD</t>
       </text>
     </comment>
     <comment ref="B14" authorId="0" shapeId="0">
@@ -1651,27 +2791,27 @@
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 10.</t>
+        <t>In 2024 this topic was Note 10. Indonesian title: UTANG USAHA</t>
       </text>
     </comment>
     <comment ref="B16" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 11.</t>
+        <t>In 2024 this topic was Note 11. Indonesian title: UTANG LAIN-LAIN</t>
       </text>
     </comment>
     <comment ref="B17" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 12.</t>
+        <t>In 2024 this topic was Note 12. Indonesian title: BEBAN AKRUAL</t>
       </text>
     </comment>
     <comment ref="B18" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 13.</t>
+        <t>In 2024 this topic was Note 13. Indonesian title: UANG MUKA PENJUALAN</t>
       </text>
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 14.</t>
+        <t>In 2024 this topic was Note 14. Indonesian title: LIABILITAS SEWA</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
@@ -1681,32 +2821,32 @@
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 15.</t>
+        <t>In 2024 this topic was Note 15. Indonesian title: PERPAJAKAN</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 16.</t>
+        <t>In 2024 this topic was Note 16. Indonesian title: UTANG PEMBIAYAAN KONSUMEN</t>
       </text>
     </comment>
     <comment ref="B23" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 17.</t>
+        <t>In 2024 this topic was Note 17. Indonesian title: UTANG BANK JANGKA PANJANG</t>
       </text>
     </comment>
     <comment ref="B24" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 18.</t>
+        <t>In 2024 this topic was Note 18. Indonesian title: UTANG OBLIGASI</t>
       </text>
     </comment>
     <comment ref="B25" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 19.</t>
+        <t>In 2024 this topic was Note 19. Indonesian title: PINJAMAN</t>
       </text>
     </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 20.</t>
+        <t>In 2024 this topic was Note 20. Indonesian title: UTANG PIHAK BERELASI</t>
       </text>
     </comment>
     <comment ref="B27" authorId="0" shapeId="0">
@@ -1716,97 +2856,97 @@
     </comment>
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 21.</t>
+        <t>In 2024 this topic was Note 21. Indonesian title: LIABILITAS IMBALAN KERJA</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 22.</t>
+        <t>In 2024 this topic was Note 22. Indonesian title: MODAL SAHAM</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 23.</t>
+        <t>In 2024 this topic was Note 23. Indonesian title: TAMBAHAN MODAL DISETOR</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 24.</t>
+        <t>In 2024 this topic was Note 24. Indonesian title: KEPENTINGAN NONPENGENDALI</t>
       </text>
     </comment>
     <comment ref="B32" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 25.</t>
+        <t>In 2024 this topic was Note 25. Indonesian title: PENDAPATAN USAHA - NETO</t>
       </text>
     </comment>
     <comment ref="B33" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 26.</t>
+        <t>In 2024 this topic was Note 26. Indonesian title: BEBAN POKOK PENDAPATAN</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 27.</t>
+        <t>In 2024 this topic was Note 27. Indonesian title: BEBAN OPERASIONAL</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 28.</t>
+        <t>In 2024 this topic was Note 28. Indonesian title: PENGHASILAN (BEBAN) LAIN-LAIN</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 29.</t>
+        <t>In 2024 this topic was Note 29. Indonesian title: PENGHASILAN KEUANGAN</t>
       </text>
     </comment>
     <comment ref="B37" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 30.</t>
+        <t>In 2024 this topic was Note 30. Indonesian title: BEBAN KEUANGAN</t>
       </text>
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 31.</t>
+        <t>In 2024 this topic was Note 31. Indonesian title: LABA NETO PER SAHAM</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 32.</t>
+        <t>In 2024 this topic was Note 32. Indonesian title: INFORMASI PIHAK BERELASI</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 33.</t>
+        <t>In 2024 this topic was Note 33. Indonesian title: INSTRUMEN KEUANGAN</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 34.</t>
+        <t>In 2024 this topic was Note 34. Indonesian title: KEBIJAKAN DAN TUJUAN MANAJEMEN RISIKO KEUANGAN</t>
       </text>
     </comment>
     <comment ref="B42" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 35.</t>
+        <t>In 2024 this topic was Note 35. Indonesian title: INFORMASI SEGMEN</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 36.</t>
+        <t>In 2024 this topic was Note 36. Indonesian title: INFORMASI TAMBAHAN ARUS KAS</t>
       </text>
     </comment>
     <comment ref="B44" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 37.</t>
+        <t>In 2024 this topic was Note 37. Indonesian title: IKATAN DAN KONTINJENSI</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 38.</t>
+        <t>In 2024 this topic was Note 38. Indonesian title: PERISTIWA SETELAH PERIODE PELAPORAN</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>In 2024, this topic was numbered Note 39.</t>
+        <t>In 2024 this topic was Note 39. Indonesian title: PENERBITAN AMENDEMEN DAN PENYESUAIAN</t>
       </text>
     </comment>
   </commentList>
@@ -1867,6 +3007,56 @@
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>2024 sub-line values extracted from 2024 AR p.244. Note 4 = Total 18,495,026,165 matches Balance Sheet. Rows for banks/deposits NOT present in 2024 are left empty.</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: 'PT Bank Central Asia Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: '(Persero) Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: '(Persero) Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: 'PT Bank Mandiri (Persero) Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: 'PT Bank IBK Indonesia Tbk' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: 'PT Bank Shinhan Indonesia' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: 'PT Bank J Trust Indonesia' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: 'PT Bank Hibank Indonesia' (substring)</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Matched from PDF p.244: 'PT Bank Syariah Indonesia Tbk' (keyword)</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>From 2024 AR p.244. Line: "PT Bank OCBC NISP Tbk - 35.000.000.000 PT Bank OCBC NISP Tbk"</t>
       </text>
     </comment>
   </commentList>
@@ -3020,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -3225,6 +4415,9 @@
           <t>PT Jaring Logistik Indonesia - PT Jaring Logistik Indonesia</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>14000000000</v>
+      </c>
       <c r="C24" s="24" t="n">
         <v>2681720721</v>
       </c>
@@ -3235,6 +4428,9 @@
           <t>PT Phatria Inti Persada - PT Phatria Inti Persada</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>207200000</v>
+      </c>
       <c r="C25" s="24" t="n">
         <v>2433027068</v>
       </c>
@@ -3572,6 +4768,9 @@
           <t>nilai tahun berjalan (Catatan ) year (Note )</t>
         </is>
       </c>
+      <c r="B56" t="n">
+        <v>-2195416449</v>
+      </c>
       <c r="C56" s="24" t="n">
         <v>1400663720</v>
       </c>
@@ -3606,6 +4805,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="30" t="inlineStr">
         <is>
@@ -3645,6 +4845,143 @@
         <v>27066764179</v>
       </c>
       <c r="C64" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 5) / Note: Rows added from 2024 Annual Report (Note 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PT Laksana Bumi Hjau - / PT Laksana Bumi Hjau</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>8325845824</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PT Lini Imaji Kreasi Ekosistem Tbk - / Ekosistem Tbk</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4966400000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PT XL Axiata Tbk - / PT XL Axiata Tbk</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2377279869</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PT Eka Mas Republik - / PT Eka Mas Republik</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>523022750</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PT Berlian Promosindo - / PT Berlian Promosindo</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>418650000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PT Wira Pamungkas Pariwara - / PT Wira Pamungkas Pariwara</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>316350000</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PT Power Telecom - / PT Power Telecom</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>371850000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PT Moving Walls Indonesia - / PT Moving Walls Indonesia</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>299145000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PT Wifian Solution - / PT Wifian Solution</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>206262420</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PT Pharos Indonesia - / PT Pharos Indonesia</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>154000000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Perusahaan Umum Damri - / Perusahaan Umum Damri</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>138901875</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PT Budaya Anak Negeri - / PT Budaya Anak Negeri</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>112800000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PT Kreasi Bilangan Sempurna - / PT Kreasi Bilangan Sempurna</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>104895000</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4574,6 +5911,7 @@
         <v>39109451500</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
@@ -4596,7 +5934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -5106,11 +6444,119 @@
         <v>39109451500</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 7 / Note: In 2024, this item was numbered Note 7</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 7) / Note: Rows added from 2024 Annual Report (Note 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PT Cahaya Surya Kemilau / - PT Cahaya Surya Kemilau</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>161854400000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PT Eka Jaya Maxima / - PT Eka Jaya Maxima</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72360000000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PT Ads Plafrom Indonesia / PT Ads Plafrom Indonesia</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5800000000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PT Pulau Pulau Media / PT Pulau Pulau Media</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1081999979</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Pengurusan izin / Licensing of network</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1747053519</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Biaya operasional / Operating cost</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Uang muka pembelian aset tetap - / Advance purchase of fixed assets</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>88384436054</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T otal / Total</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>393686379659</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>jasa pembangunan FTTH sebesar Rp / in accordance with agreement</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>120000000000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>uang muka untuk biaya sewa tersebut sebesar the rental fee was Rp / in accordance</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5845,6 +7291,9 @@
           <t>Tanah - - - Land</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>10589785000</v>
+      </c>
       <c r="C23" s="24" t="n">
         <v>10589785000</v>
       </c>
@@ -5855,6 +7304,9 @@
           <t>Bangunan - - - Buildings</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>19037072008</v>
+      </c>
       <c r="C24" s="24" t="n">
         <v>19037072008</v>
       </c>
@@ -5865,6 +7317,9 @@
           <t>Kendaraan - - - Vehicles</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>3180395917</v>
+      </c>
       <c r="C25" s="24" t="n">
         <v>3180395917</v>
       </c>
@@ -5875,6 +7330,9 @@
           <t>Peralatan - Equipments</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>4886499391</v>
+      </c>
       <c r="C26" s="24" t="n">
         <v>4886499391</v>
       </c>
@@ -5892,6 +7350,9 @@
           <t>dan perabotan - Fixtures and furnitures</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>1673173969</v>
+      </c>
       <c r="C28" s="24" t="n">
         <v>1673173969</v>
       </c>
@@ -5912,6 +7373,9 @@
           <t>Project equipments Project equipments</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>1360567021010</v>
+      </c>
       <c r="C30" s="24" t="n">
         <v>1360567021010</v>
       </c>
@@ -5953,6 +7417,9 @@
           <t>Project equipments - Project equipments</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>934874153011</v>
+      </c>
       <c r="C35" s="24" t="n">
         <v>934874153011</v>
       </c>
@@ -6001,6 +7468,9 @@
           <t>Bangunan - - - Buildings</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>4897364444</v>
+      </c>
       <c r="C41" s="24" t="n">
         <v>4897364444</v>
       </c>
@@ -6011,6 +7481,9 @@
           <t>Kendaraan - - - Vehicles</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>959020385</v>
+      </c>
       <c r="C42" s="24" t="n">
         <v>959020385</v>
       </c>
@@ -6021,6 +7494,9 @@
           <t>Peralatan - Equipments</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>2742641366</v>
+      </c>
       <c r="C43" s="24" t="n">
         <v>2742641366</v>
       </c>
@@ -6038,6 +7514,9 @@
           <t>perabotan - - Fixtures and furnitures</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>1136463484</v>
+      </c>
       <c r="C45" s="24" t="n">
         <v>1136463484</v>
       </c>
@@ -6058,6 +7537,9 @@
           <t>Project equipments - Project equipments</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>224247148511</v>
+      </c>
       <c r="C47" s="24" t="n">
         <v>224247148511</v>
       </c>
@@ -6078,6 +7560,9 @@
           <t>Total - Tota l</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>312744637652</v>
+      </c>
       <c r="C49" s="24" t="n">
         <v>312744637652</v>
       </c>
@@ -6088,6 +7573,9 @@
           <t>Nilai Buku Neto Net Book Value</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>2299004659722</v>
+      </c>
       <c r="C50" s="24" t="n">
         <v>2299004659722</v>
       </c>
@@ -6201,6 +7689,7 @@
         <v>969042209112</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
@@ -6582,6 +8071,9 @@
           <t>Captive Portal Software - - Portal Software</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>2000000000</v>
+      </c>
       <c r="C49" s="24" t="n">
         <v>2000000000</v>
       </c>
@@ -6592,6 +8084,9 @@
           <t>Perangkat lunak - - Software</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>10952800395</v>
+      </c>
       <c r="C50" s="24" t="n">
         <v>10952800395</v>
       </c>
@@ -6650,6 +8145,9 @@
           <t>Captive Portal Software - - Portal Software</t>
         </is>
       </c>
+      <c r="B57" t="n">
+        <v>1860158370</v>
+      </c>
       <c r="C57" s="24" t="n">
         <v>1860158370</v>
       </c>
@@ -6680,6 +8178,9 @@
           <t>Nilai Buku Neto Net Book Value</t>
         </is>
       </c>
+      <c r="B60" t="n">
+        <v>11092642025</v>
+      </c>
       <c r="C60" s="24" t="n">
         <v>11092642025</v>
       </c>
@@ -6691,6 +8192,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
@@ -7211,7 +8713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7376,7 +8878,9 @@
           <t>Indonesia - PT Optictimes Teknologi Indonesia</t>
         </is>
       </c>
-      <c r="B21" t="n"/>
+      <c r="B21" t="n">
+        <v>1751580000</v>
+      </c>
       <c r="C21" s="24" t="n">
         <v>20570062678</v>
       </c>
@@ -7442,7 +8946,9 @@
           <t>PT Era Media Sejahtera Tbk - PT Era Media Sejahtera Tbk</t>
         </is>
       </c>
-      <c r="B27" t="n"/>
+      <c r="B27" t="n">
+        <v>7608730069</v>
+      </c>
       <c r="C27" s="24" t="n">
         <v>1562243297</v>
       </c>
@@ -7460,7 +8966,9 @@
           <t>(KOPINDOSAT) - (KOPINDOSAT)</t>
         </is>
       </c>
-      <c r="B29" t="n"/>
+      <c r="B29" t="n">
+        <v>6251564087</v>
+      </c>
       <c r="C29" s="24" t="n">
         <v>6251564087</v>
       </c>
@@ -7471,7 +8979,9 @@
           <t>PT Cahaya Agung Oetama - PT Cahaya Agung Oetama</t>
         </is>
       </c>
-      <c r="B30" t="n"/>
+      <c r="B30" t="n">
+        <v>3535762908</v>
+      </c>
       <c r="C30" s="24" t="n">
         <v>3535762908</v>
       </c>
@@ -7482,7 +8992,9 @@
           <t>PT Kereta Api Indonesia (Persero) - PT Kereta Api Indonesia (Persero)</t>
         </is>
       </c>
-      <c r="B31" t="n"/>
+      <c r="B31" t="n">
+        <v>9342535417</v>
+      </c>
       <c r="C31" s="24" t="n">
         <v>9342535417</v>
       </c>
@@ -7493,7 +9005,9 @@
           <t>PT Laksana Bumi Berseri - PT Laksana Bumi Berseri</t>
         </is>
       </c>
-      <c r="B32" t="n"/>
+      <c r="B32" t="n">
+        <v>2542125562</v>
+      </c>
       <c r="C32" s="24" t="n">
         <v>2542125562</v>
       </c>
@@ -7504,7 +9018,9 @@
           <t>PT Cahaya Surya Kemilau - PT Cahaya Surya Kemilau</t>
         </is>
       </c>
-      <c r="B33" t="n"/>
+      <c r="B33" t="n">
+        <v>2508957725</v>
+      </c>
       <c r="C33" s="24" t="n">
         <v>2508957725</v>
       </c>
@@ -7515,7 +9031,9 @@
           <t>PT Knet Indonesia - PT Knet Indonesia</t>
         </is>
       </c>
-      <c r="B34" t="n"/>
+      <c r="B34" t="n">
+        <v>1634159415</v>
+      </c>
       <c r="C34" s="24" t="n">
         <v>1634159415</v>
       </c>
@@ -7576,7 +9094,9 @@
           <t>Belum jatuh tempo Current</t>
         </is>
       </c>
-      <c r="B40" t="n"/>
+      <c r="B40" t="n">
+        <v>3407267358</v>
+      </c>
       <c r="C40" s="24" t="n">
         <v>339154108185</v>
       </c>
@@ -7594,7 +9114,9 @@
           <t>Kurang dari hari - Less than days</t>
         </is>
       </c>
-      <c r="B42" t="n"/>
+      <c r="B42" t="n">
+        <v>12559321007</v>
+      </c>
       <c r="C42" s="24" t="n">
         <v>66881116512</v>
       </c>
@@ -7605,7 +9127,9 @@
           <t>- hari - days</t>
         </is>
       </c>
-      <c r="B43" t="n"/>
+      <c r="B43" t="n">
+        <v>3714322561</v>
+      </c>
       <c r="C43" s="24" t="n">
         <v>298001443</v>
       </c>
@@ -7616,7 +9140,9 @@
           <t>- hari - days</t>
         </is>
       </c>
-      <c r="B44" t="n"/>
+      <c r="B44" t="n">
+        <v>13320459361</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>586156660</v>
       </c>
@@ -7792,11 +9318,199 @@
         <v>-24174474942</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 10 / Note: In 2024, this item was numbered Note 10</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 10) / Note: Rows added from 2024 Annual Report (Note 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PT Solidsteel Tamajaya Indonesia / - PT Solidsteel Tamajaya Indonesia</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>915147270</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Shinta Sriwijaya &amp; Co / Shinta Sriwijaya &amp; Co</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>855000000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PT Winnow Wastu Wilasa / PT Winnow Wastu Wilasa</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>661560000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PT Paramitha Adikarya Tekno / - PT Paramitha Adikarya Tekno</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>610197416</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PT Nunut Eldana Prima / - PT Nunut Eldana Prima</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>580362256</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PT Sompo Insurance / PT Sompo Insurance</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>421740410</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PT Aquila Wijaya Teknik / PT Aquila Wijaya Teknik</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>404270412</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PT Kalibesar Raya Utama / PT Kalibesar Raya Utama</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>372472890</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PT Bisnis Ini Sinergi / - PT Bisnis Ini Sinergi</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>113217786</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PT Ilab Komunikasi Indonesia - / PT Ilab Komunikasi Indonesia</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>60713000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PT Lini Imaji Kreasi Ekosistem Tbk - / PT Lini Imaji Kreasi Ekosistem Tbk</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2865976000</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PT IP Network Solusindo - / PT IP Network Solusindo</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1908081619</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PT Pradikta Unggul - / PT Pradikta Unggul</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>842094955</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PT Davon Media Teknologi - / PT Davon Media Teknologi</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>561577121</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PT Multipolar Technology - / PT Multipolar Technology</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>532519070</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CV Infra Media Solusindo - / CV Infra Media Solusindo</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>359069650</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PT Telekomindo Global Mandiri - / PT Telekomindo Global Mandiri</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>304362000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PT Sepur Berkah Komunikasi - / PT Sepur Berkah Komunikasi</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>164596500</v>
       </c>
     </row>
   </sheetData>
@@ -7814,7 +9528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -8017,6 +9731,9 @@
           <t>PT Maju Bersama Gemilang - PT Maju Bersama Gemilang</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>167425000000</v>
+      </c>
       <c r="C25" s="24" t="n">
         <v>6066438000</v>
       </c>
@@ -8306,7 +10023,9 @@
           <t>PT Prambanan Investasi Sukses PT Prambanan Investasi Sukses</t>
         </is>
       </c>
-      <c r="B56" t="n"/>
+      <c r="B56" t="n">
+        <v>151950000000</v>
+      </c>
       <c r="C56" s="24" t="n">
         <v>154856043750</v>
       </c>
@@ -8328,7 +10047,9 @@
           <t>Beban bunga (Catatan ) Interest expense (Note )</t>
         </is>
       </c>
-      <c r="B58" t="n"/>
+      <c r="B58" t="n">
+        <v>7072875000</v>
+      </c>
       <c r="C58" s="24" t="n">
         <v>12017250000</v>
       </c>
@@ -8339,7 +10060,9 @@
           <t>Pajak penghasilan atas bunga Income tax on interest</t>
         </is>
       </c>
-      <c r="B59" t="n"/>
+      <c r="B59" t="n">
+        <v>-1060931250</v>
+      </c>
       <c r="C59" s="24" t="n">
         <v>-1802587500</v>
       </c>
@@ -8380,11 +10103,29 @@
         <v>-24174474942</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 11 / Note: In 2024, this item was numbered Note 11</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 11) / Note: Rows added from 2024 Annual Report (Note 11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>S ubtotal / - Subtotal</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>301212468808</v>
       </c>
     </row>
   </sheetData>
@@ -8836,7 +10577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -9226,7 +10967,9 @@
           <t>Retribusi Retribution</t>
         </is>
       </c>
-      <c r="B53" t="n"/>
+      <c r="B53" t="n">
+        <v>4742647452</v>
+      </c>
       <c r="C53" s="24" t="n">
         <v>21240100854</v>
       </c>
@@ -9259,7 +11002,9 @@
           <t>Jasa professional Professional fee</t>
         </is>
       </c>
-      <c r="B56" t="n"/>
+      <c r="B56" t="n">
+        <v>333550000</v>
+      </c>
       <c r="C56" s="24" t="n">
         <v>2098937005</v>
       </c>
@@ -9323,11 +11068,29 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 12 / Note: In 2024, this item was numbered Note 12</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 12) / Note: Rows added from 2024 Annual Report (Note 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Utilitas / - Utilitas</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>33517500</v>
       </c>
     </row>
   </sheetData>
@@ -9795,6 +11558,9 @@
           <t>Bagian jangka panjang Long-term portion</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>127559944472</v>
+      </c>
       <c r="C53" s="24" t="n">
         <v>136748630794</v>
       </c>
@@ -9869,6 +11635,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
@@ -9891,7 +11658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -10236,6 +12003,9 @@
           <t>Bagian jangka panjang Long-term portion</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>158533723977</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>7891261422</v>
       </c>
@@ -10407,11 +12177,49 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 14 / Note: In 2024, this item was numbered Note 14</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 14) / Note: Rows added from 2024 Annual Report (Note 14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gedung kantor / Office building</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2492608193</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dark fiber / Dark fiber</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>5939208780</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Tanah / Land</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>268509380095</v>
       </c>
     </row>
   </sheetData>
@@ -10933,7 +12741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -11069,6 +12877,9 @@
           <t>Pajak Pertambahan Nilai - Value Added Tax</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>1592818184</v>
+      </c>
       <c r="C18" s="24" t="n">
         <v>55772852991</v>
       </c>
@@ -11086,6 +12897,9 @@
           <t>Pajak Pertambahan Nilai Value Added Tax</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>16256239877</v>
+      </c>
       <c r="C20" s="24" t="n">
         <v>39618838784</v>
       </c>
@@ -11113,6 +12927,9 @@
           <t>Total Total</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>16256512269</v>
+      </c>
       <c r="C23" s="24" t="n">
         <v>95405164859</v>
       </c>
@@ -11136,6 +12953,9 @@
         <is>
           <t>Pajak Pertambahan Nilai - Value Added Tax</t>
         </is>
+      </c>
+      <c r="B26" t="n">
+        <v>23472686352</v>
       </c>
       <c r="C26" s="24" t="n">
         <v>23472686352</v>
@@ -11207,6 +13027,9 @@
           <t>Sub-total Sub-total</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>40185553486</v>
+      </c>
       <c r="C34" s="24" t="n">
         <v>64616616239</v>
       </c>
@@ -11224,6 +13047,9 @@
           <t>Pajak Pertambahan Nilai Value Added Tax</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>31370296819</v>
+      </c>
       <c r="C36" s="24" t="n">
         <v>58653193067</v>
       </c>
@@ -11233,6 +13059,9 @@
         <is>
           <t>Pajak Final Final Tax</t>
         </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6356865</v>
       </c>
       <c r="C37" s="24" t="n">
         <v>6356865</v>
@@ -11304,6 +13133,9 @@
           <t>Sub-total Sub-total</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>72184515853</v>
+      </c>
       <c r="C45" s="24" t="n">
         <v>127609203629</v>
       </c>
@@ -11314,6 +13146,9 @@
           <t>Total Total</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>112370069339</v>
+      </c>
       <c r="C46" s="24" t="n">
         <v>192225819868</v>
       </c>
@@ -11345,6 +13180,9 @@
           <t>Perusahaan The Company</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>-13049014880</v>
+      </c>
       <c r="C50" s="24" t="n">
         <v>-47049942500</v>
       </c>
@@ -11355,6 +13193,9 @@
           <t>Entitas Anak Subsidiaries</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>-25237579300</v>
+      </c>
       <c r="C51" s="24" t="n">
         <v>-25760183502</v>
       </c>
@@ -11365,6 +13206,9 @@
           <t>Total pajak kini Total current tax</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>-38286594180</v>
+      </c>
       <c r="C52" s="24" t="n">
         <v>-72810126002</v>
       </c>
@@ -11382,6 +13226,9 @@
           <t>Perusahaan The Company</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>-327771270</v>
+      </c>
       <c r="C54" s="24" t="n">
         <v>-139104006</v>
       </c>
@@ -11392,6 +13239,9 @@
           <t>Entitas Anak Subsidiaries</t>
         </is>
       </c>
+      <c r="B55" t="n">
+        <v>5143393536</v>
+      </c>
       <c r="C55" s="24" t="n">
         <v>1792447822</v>
       </c>
@@ -11402,6 +13252,9 @@
           <t>Total pajak tangguhan Total deferred tax</t>
         </is>
       </c>
+      <c r="B56" t="n">
+        <v>4815622266</v>
+      </c>
       <c r="C56" s="24" t="n">
         <v>1653343816</v>
       </c>
@@ -11419,6 +13272,9 @@
           <t>neto</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>-43102216446</v>
+      </c>
       <c r="C58" s="24" t="n">
         <v>-71156782186</v>
       </c>
@@ -11458,11 +13314,59 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 15 / Note: In 2024, this item was numbered Note 15</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 15) / Note: Rows added from 2024 Annual Report (Note 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Perusahaan / The Company</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>13049014880</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Entitas Anak / Subsidiaries</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>25237579300</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Total pajak kini / Total current tax</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>38286594180</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>penghasilan - neto / expense - net</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>43102216446</v>
       </c>
     </row>
   </sheetData>
@@ -11480,7 +13384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -11602,6 +13506,9 @@
           <t>PT BCA Finance PT BCA Finance</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1112682972</v>
+      </c>
       <c r="C16" s="24" t="n">
         <v>1517135551</v>
       </c>
@@ -11612,6 +13519,9 @@
           <t>PT Maybank Indonesia Finance - PT Maybank Indonesia Finance</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>386633823</v>
+      </c>
       <c r="C17" s="24" t="n">
         <v>1459977000</v>
       </c>
@@ -11697,6 +13607,9 @@
           <t>Jumlah fasilitas pembiayaan : Rp Total financing facility : Rp</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>409762500</v>
+      </c>
       <c r="C27" s="24" t="n">
         <v>378525000</v>
       </c>
@@ -11742,6 +13655,9 @@
           <t>Jumlah fasilitas pembiayaan : Rp Total financing facility : Rp</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>409762500</v>
+      </c>
       <c r="C33" s="24" t="n">
         <v>378525000</v>
       </c>
@@ -11787,6 +13703,9 @@
           <t>Jumlah fasilitas pembiayaan : Rp Total financing facility : Rp</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>409762500</v>
+      </c>
       <c r="C39" s="24" t="n">
         <v>462315000</v>
       </c>
@@ -11825,6 +13744,9 @@
           <t>Jumlah fasilitas pembiayaan : Rp Total financing facility : Rp</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>409762500</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>315315000</v>
       </c>
@@ -11863,6 +13785,9 @@
           <t>Jumlah fasilitas pembiayaan : Rp Total financing facility : Rp</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>577480800</v>
+      </c>
       <c r="C49" s="24" t="n">
         <v>307965000</v>
       </c>
@@ -11901,6 +13826,9 @@
           <t>Jumlah fasilitas pembiayaan : Rp Total financing facility : Rp</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>577480800</v>
+      </c>
       <c r="C54" s="24" t="n">
         <v>459595500</v>
       </c>
@@ -11940,11 +13868,29 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 16 / Note: In 2024, this item was numbered Note 16</t>
         </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 16) / Note: Rows added from 2024 Annual Report (Note 16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Jumlah fasilitas pembiayaan : Rp</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>703692480</v>
       </c>
     </row>
   </sheetData>
@@ -11962,7 +13908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -12271,6 +14217,9 @@
           <t>PT Bank Hibank Indonesia PT Bank Hibank Indonesia</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>50000000000</v>
+      </c>
       <c r="C41" s="24" t="n">
         <v>170000000000</v>
       </c>
@@ -12301,6 +14250,9 @@
           <t>PT BPR Kirana Indonesia - PT BPR Kirana Indonesia</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>3294900000</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>3294900000</v>
       </c>
@@ -12318,6 +14270,9 @@
           <t>diamortisasi expense amortized</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>-138055277673</v>
+      </c>
       <c r="C46" s="24" t="n">
         <v>-4031000000</v>
       </c>
@@ -12416,6 +14371,9 @@
           <t>Plafond : Rp Plafond : Rp</t>
         </is>
       </c>
+      <c r="B57" t="n">
+        <v>7800000000</v>
+      </c>
       <c r="C57" s="24" t="n">
         <v>90000000000</v>
       </c>
@@ -12462,11 +14420,49 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 17 / Note: In 2024, this item was numbered Note 17</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 17) / Note: Rows added from 2024 Annual Report (Note 17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PT Bank J Trust Indonesia / PT Bank J Trust Indonesia</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>149875000004</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>(Persero) Tbk - / (Persero) Tbk</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>212476592826</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>diamortisasi / expense amortized</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>-2001000000</v>
       </c>
     </row>
   </sheetData>
@@ -12484,7 +14480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -12620,6 +14616,9 @@
           <t>Ob ligasi II Seri A - Series A Bonds II</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>150500000000</v>
+      </c>
       <c r="C18" s="24" t="n">
         <v>793440000000</v>
       </c>
@@ -12630,6 +14629,9 @@
           <t>Ob ligasi II Seri B - Series B Bonds II</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>299000000000</v>
+      </c>
       <c r="C19" s="24" t="n">
         <v>456560000000</v>
       </c>
@@ -12640,6 +14642,9 @@
           <t>Ob ligasi Seri C - Series C Bonds</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>150500000000</v>
+      </c>
       <c r="C20" s="24" t="n">
         <v>150500000000</v>
       </c>
@@ -12670,6 +14675,9 @@
           <t>Bu nga obligasi Bonds interests</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>17342377778</v>
+      </c>
       <c r="C23" s="24" t="n">
         <v>64246061110</v>
       </c>
@@ -12711,7 +14719,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166632590847</v>
+        <v>-166632590847</v>
       </c>
       <c r="C27" s="24" t="n">
         <v>852473632493</v>
@@ -12830,6 +14838,9 @@
           <t>dalam jumlah sebesar Rp . amount of Rp .</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>299000000000</v>
+      </c>
       <c r="C42" s="24" t="n">
         <v>150500000000</v>
       </c>
@@ -12861,6 +14872,9 @@
           <t>sebesar Rp . Rp .</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>150500000000</v>
+      </c>
       <c r="C46" s="24" t="n">
         <v>299000000000</v>
       </c>
@@ -12987,11 +15001,49 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 18 / Note: In 2024, this item was numbered Note 18</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 18) / Note: Rows added from 2024 Annual Report (Note 18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B iaya emisi obligasi / - Bond issuence cost</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>-3257302844</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>tahun / - maturities</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>166632590847</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>masyarakat dengan nilai nominal sebesar a n o m i n a l v a l u e o f R p / .</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -13295,6 +15347,9 @@
           <t>Finance Indonesia Finance Indonesia</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>50751274989</v>
+      </c>
       <c r="C39" s="24" t="n">
         <v>114532428116</v>
       </c>
@@ -13305,6 +15360,9 @@
           <t>PT KDB Tifa Finance Tbk PT KDB Tifa Finance Tbk</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>32194401912</v>
+      </c>
       <c r="C40" s="24" t="n">
         <v>68895670418</v>
       </c>
@@ -13325,6 +15383,9 @@
           <t>PT Radana Bhasakara Finance Tbk - PT Radana Bhasakara Finance Tbk</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>24408000000</v>
+      </c>
       <c r="C42" s="24" t="n">
         <v>24408000000</v>
       </c>
@@ -13335,6 +15396,9 @@
           <t>PT Akulaku Finance Indonesia - PT Akulaku Finance Indonesia</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>8769000000</v>
+      </c>
       <c r="C43" s="24" t="n">
         <v>8769000000</v>
       </c>
@@ -13345,6 +15409,9 @@
           <t>PT Pegadaian (Persero) - PT Pegadaian (Persero)</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>2000000000</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>2000000000</v>
       </c>
@@ -13436,6 +15503,9 @@
           <t>Indonesia sebesar Rp . Pembiayaan ini amounting to Rp . This financing bears</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>28680624000</v>
+      </c>
       <c r="C54" s="24" t="n">
         <v>28680624000</v>
       </c>
@@ -13503,6 +15573,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
@@ -13916,6 +15987,9 @@
           <t>Saldo awal Beginning balance</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>7853750389</v>
+      </c>
       <c r="C54" s="24" t="n">
         <v>63063149392</v>
       </c>
@@ -13926,6 +16000,9 @@
           <t>Penambahan Additional</t>
         </is>
       </c>
+      <c r="B55" t="n">
+        <v>54765264905</v>
+      </c>
       <c r="C55" s="24" t="n">
         <v>360832265963</v>
       </c>
@@ -13946,6 +16023,9 @@
           <t>Beban bunga (Catatan ) Interest expense (Note )</t>
         </is>
       </c>
+      <c r="B57" t="n">
+        <v>522510703</v>
+      </c>
       <c r="C57" s="24" t="n">
         <v>391883027</v>
       </c>
@@ -13956,6 +16036,9 @@
           <t>Pajak penghasilan atas bunga Income tax on interest</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>-78376605</v>
+      </c>
       <c r="C58" s="24" t="n">
         <v>-58782454</v>
       </c>
@@ -14004,6 +16087,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
@@ -15099,7 +17183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -15508,6 +17592,9 @@
           <t>B iaya jasa kini . . Current service cos t</t>
         </is>
       </c>
+      <c r="B57" t="n">
+        <v>1011999595</v>
+      </c>
       <c r="C57" s="24" t="n">
         <v>633496111</v>
       </c>
@@ -15518,6 +17605,9 @@
           <t>Biaya bunga Interest cost</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>169193825</v>
+      </c>
       <c r="C58" s="24" t="n">
         <v>195223732</v>
       </c>
@@ -15569,11 +17659,49 @@
         <v>3121413272</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 21 / Note: In 2024, this item was numbered Note 21</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 21) / Note: Rows added from 2024 Annual Report (Note 21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>laba rugi (Catatan / )</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1181193420</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>komprehensif lain / comprehensive income</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-538204957</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T otal / Total</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>642988463</v>
       </c>
     </row>
   </sheetData>
@@ -15793,6 +17921,9 @@
           <t>kurang dari %) % Public (each below %)</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>1177132298</v>
+      </c>
       <c r="C27" s="24" t="n">
         <v>2460297086</v>
       </c>
@@ -16043,6 +18174,9 @@
           <t>sebanyak lembar saham yang dilakukan made by PT Investasi Sukses Bersama (“ISB”).</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>1182222820</v>
+      </c>
       <c r="C58" s="24" t="n">
         <v>4718710236</v>
       </c>
@@ -16085,6 +18219,7 @@
         <v>5308549015</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
@@ -16107,7 +18242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -16451,6 +18586,9 @@
           <t>tahun (Catatan ) in (Note )</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>60897018740</v>
+      </c>
       <c r="C46" s="24" t="n">
         <v>189018110000</v>
       </c>
@@ -16569,6 +18707,9 @@
           <t>Pengampunan pajak Tax amnesty</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>3125956639</v>
+      </c>
       <c r="C59" s="24" t="n">
         <v>3125956639</v>
       </c>
@@ -16610,11 +18751,39 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 23 / Note: In 2024, this item was numbered Note 23</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 23) / Note: Rows added from 2024 Annual Report (Note 23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PMTHMETD (Catatan / )</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>17632494000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Biaya emisi saham (Catatan / c)</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>-3532387928</v>
       </c>
     </row>
   </sheetData>
@@ -16632,7 +18801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -16764,6 +18933,9 @@
           <t>PT Gawai Maju Indonesia PT Gawai Maju Indonesia</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>-1752368</v>
+      </c>
       <c r="C17" s="24" t="n">
         <v>-937232587</v>
       </c>
@@ -16774,6 +18946,9 @@
           <t>PT Jejaring Digital Utama PT Jejaring Digital Utama</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>606016</v>
+      </c>
       <c r="C18" s="24" t="n">
         <v>259807246</v>
       </c>
@@ -16804,6 +18979,9 @@
           <t>PT Kreasi Kode Digital PT Kreasi Kode Digital</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>258619980</v>
+      </c>
       <c r="C21" s="24" t="n">
         <v>-2143882825</v>
       </c>
@@ -16821,6 +18999,9 @@
           <t>PT Sinergi Apta Media - PT Sinergi Apta Media</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>198785380</v>
+      </c>
       <c r="C23" s="24" t="n">
         <v>198785380</v>
       </c>
@@ -16831,6 +19012,9 @@
           <t>PT Sinergi Aplikasi Akurat - PT Sinergi Aplikasi Akurat</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>149318550</v>
+      </c>
       <c r="C24" s="24" t="n">
         <v>149318550</v>
       </c>
@@ -16841,6 +19025,9 @@
           <t>PT Media Digital Selaras - - PT Media Digital Selaras</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>150462500</v>
+      </c>
       <c r="C25" s="24" t="n">
         <v>150462500</v>
       </c>
@@ -16851,6 +19038,9 @@
           <t>PT Laper Nih Indonesia - - PT Laper Nih Indonesia</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>-4577598</v>
+      </c>
       <c r="C26" s="24" t="n">
         <v>-4577598</v>
       </c>
@@ -16861,6 +19051,9 @@
           <t>PT Aspek Media Indonesia - PT Aspek Media Indonesia</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>-19707051</v>
+      </c>
       <c r="C27" s="24" t="n">
         <v>-19707051</v>
       </c>
@@ -16871,6 +19064,9 @@
           <t>PT Sinergi Media Digital - PT Sinergi Media Digital</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>-25420975</v>
+      </c>
       <c r="C28" s="24" t="n">
         <v>-25420975</v>
       </c>
@@ -16881,6 +19077,9 @@
           <t>PT Integrasi Media Terkini - PT Integrasi Media Terkini</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>-52200322</v>
+      </c>
       <c r="C29" s="24" t="n">
         <v>-52200322</v>
       </c>
@@ -16891,6 +19090,9 @@
           <t>PT Laju Inti Digital - -- PT Laju Inti Digital</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>-173074519</v>
+      </c>
       <c r="C30" s="24" t="n">
         <v>-173074519</v>
       </c>
@@ -17157,11 +19359,49 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 24 / Note: In 2024, this item was numbered Note 24</t>
         </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 24) / Note: Rows added from 2024 Annual Report (Note 24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PT Solusi Pariwisata Digital / PT Solusi Pariwisata Digital</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>-140794054</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PT Jaringan Infra Andalan / PT Jaringan Infra Andalan</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>-158847364</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PT Integrasi Jaringan Ekosistem - / PT Integrasi Jaringan Ekosistem</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2180891352</v>
       </c>
     </row>
   </sheetData>
@@ -17179,7 +19419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -17311,6 +19551,9 @@
           <t>PT Gawai Maju Indonesia PT Gawai Maju Indonesia</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>111355179154</v>
+      </c>
       <c r="C17" s="24" t="n">
         <v>-937232587</v>
       </c>
@@ -17341,6 +19584,9 @@
           <t>PT Solusi Jaringan Nusantara PT Solusi Jaringan Nusantara</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>34580000000</v>
+      </c>
       <c r="C20" s="24" t="n">
         <v>-246216364</v>
       </c>
@@ -17472,6 +19718,9 @@
           <t>Bandwidth Bandwidth</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>227195231783</v>
+      </c>
       <c r="C34" s="24" t="n">
         <v>560850590051</v>
       </c>
@@ -17492,6 +19741,9 @@
           <t>Sewa core Core lease</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>101903348841</v>
+      </c>
       <c r="C36" s="24" t="n">
         <v>96420658631</v>
       </c>
@@ -17502,6 +19754,9 @@
           <t>Colocation Colocation</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>2363155540</v>
+      </c>
       <c r="C37" s="24" t="n">
         <v>2558194782</v>
       </c>
@@ -17529,6 +19784,9 @@
           <t>Iklan Advertising</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>320388967114</v>
+      </c>
       <c r="C40" s="24" t="n">
         <v>459466094623</v>
       </c>
@@ -17549,6 +19807,9 @@
           <t>Potongan harga Discount</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>-5076527006</v>
+      </c>
       <c r="C42" s="24" t="n">
         <v>-9287068715</v>
       </c>
@@ -17673,6 +19934,9 @@
           <t>Investindo - % % Investindo</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>91782841492</v>
+      </c>
       <c r="C58" s="24" t="n">
         <v>91782841492</v>
       </c>
@@ -17683,6 +19947,9 @@
           <t>PT XL Axiata Tbk - % % PT XL Axiata Tbk</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>74405832479</v>
+      </c>
       <c r="C59" s="24" t="n">
         <v>74405832479</v>
       </c>
@@ -17704,11 +19971,49 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 25 / Note: In 2024, this item was numbered Note 25</t>
         </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 25) / Note: Rows added from 2024 Annual Report (Note 25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Manage telco service / - Manage telco service</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>25079825000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Portal web dan platform digital - / Web portal and digital platform</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>57460084820</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Bersama - / % Bersama</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>30568475676</v>
       </c>
     </row>
   </sheetData>
@@ -17726,7 +20031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -17879,6 +20184,9 @@
           <t>ketiga advertising services</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>60029971450</v>
+      </c>
       <c r="C20" s="24" t="n">
         <v>77964962036</v>
       </c>
@@ -17899,6 +20207,9 @@
           <t>Portal web dan platform digital - Portal web and platform digital</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>107535561419</v>
+      </c>
       <c r="C22" s="24" t="n">
         <v>8561407448</v>
       </c>
@@ -18283,11 +20594,29 @@
         <v>986305965</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 26 / Note: In 2024, this item was numbered Note 26</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 26) / Note: Rows added from 2024 Annual Report (Note 26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Telekomunikasi / Telecommunication</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>89515154515</v>
       </c>
     </row>
   </sheetData>
@@ -18305,7 +20634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -18684,6 +21013,9 @@
           <t>Gaji dan tunjangan Salaries and allowances</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>16953228623</v>
+      </c>
       <c r="C45" s="24" t="n">
         <v>71804723713</v>
       </c>
@@ -18701,6 +21033,9 @@
           <t>pemasaran and marketing</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>1390829400</v>
+      </c>
       <c r="C47" s="24" t="n">
         <v>22386857618</v>
       </c>
@@ -18711,6 +21046,9 @@
           <t>Beban pajak Tax expense</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>170866849</v>
+      </c>
       <c r="C48" s="24" t="n">
         <v>21961696251</v>
       </c>
@@ -18731,6 +21069,9 @@
           <t>Penyusutan (Catatan ) Depreciation (Note )</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>18460627789</v>
+      </c>
       <c r="C50" s="24" t="n">
         <v>12798054573</v>
       </c>
@@ -18741,6 +21082,9 @@
           <t>Jasa professional Professional fee</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>3283512475</v>
+      </c>
       <c r="C51" s="24" t="n">
         <v>12202826840</v>
       </c>
@@ -18751,6 +21095,9 @@
           <t>Transportasi dan perjalanan dinas Transportation and business trip</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>4114196624</v>
+      </c>
       <c r="C52" s="24" t="n">
         <v>9014805710</v>
       </c>
@@ -18761,6 +21108,9 @@
           <t>Asuransi Insurance</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>4580405309</v>
+      </c>
       <c r="C53" s="24" t="n">
         <v>5990859358</v>
       </c>
@@ -18771,6 +21121,9 @@
           <t>Administrasi efek Securities administration</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>424638146</v>
+      </c>
       <c r="C54" s="24" t="n">
         <v>5805888070</v>
       </c>
@@ -18825,6 +21178,9 @@
           <t>dan listrik and electricity</t>
         </is>
       </c>
+      <c r="B60" t="n">
+        <v>1335665963</v>
+      </c>
       <c r="C60" s="24" t="n">
         <v>1317687720</v>
       </c>
@@ -18835,6 +21191,9 @@
           <t>Perlengkapan Equipment</t>
         </is>
       </c>
+      <c r="B61" t="n">
+        <v>69584615</v>
+      </c>
       <c r="C61" s="24" t="n">
         <v>1136059655</v>
       </c>
@@ -18845,6 +21204,9 @@
           <t>Natura Nature</t>
         </is>
       </c>
+      <c r="B62" t="n">
+        <v>464721207</v>
+      </c>
       <c r="C62" s="24" t="n">
         <v>1123174056</v>
       </c>
@@ -18855,15 +21217,76 @@
           <t>Alat tulis dan cetakan Stationery and prints</t>
         </is>
       </c>
+      <c r="B63" t="n">
+        <v>522617860</v>
+      </c>
       <c r="C63" s="24" t="n">
         <v>986305965</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 27 / Note: In 2024, this item was numbered Note 27</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 27) / Note: Rows added from 2024 Annual Report (Note 27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Komisi - / Commission</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>78014659</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Perizinan / License</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10157803693</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jamuan dan sumbangan / Entertain and donations</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2453754352</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sewa / Rent</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1642856856</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Pemeliharaan dan perawatan / Maintenance and care</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>337113233</v>
       </c>
     </row>
   </sheetData>
@@ -18881,7 +21304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -19010,6 +21433,9 @@
           <t>(Catatan ) - entity (Note )</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>221090632</v>
+      </c>
       <c r="C17" s="24" t="n">
         <v>45181911097</v>
       </c>
@@ -19044,6 +21470,9 @@
           <t>nilai piutang usaha (Catatan ) - for trade receivables (Note )</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>-1087001595</v>
+      </c>
       <c r="C21" s="24" t="n">
         <v>2017962420</v>
       </c>
@@ -19071,6 +21500,9 @@
           <t>Penghapusan piutang usaha - Write-off of trade receivables</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>-760738885</v>
+      </c>
       <c r="C24" s="24" t="n">
         <v>-2155564385</v>
       </c>
@@ -19356,11 +21788,29 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 28 / Note: In 2024, this item was numbered Note 28</t>
         </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 28) / Note: Rows added from 2024 Annual Report (Note 28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Laba pelepasan entitas anak - / Profit on disposal of subsidiary entity</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>445566411</v>
       </c>
     </row>
   </sheetData>
@@ -19378,7 +21828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -19612,6 +22062,9 @@
           <t>dan jasa giro bank giro service</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>538954781</v>
+      </c>
       <c r="C29" s="24" t="n">
         <v>34273445654</v>
       </c>
@@ -19853,11 +22306,29 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 29 / Note: In 2024, this item was numbered Note 29</t>
         </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 29) / Note: Rows added from 2024 Annual Report (Note 29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Penghasilan bunga kontraktrual - / Contractual interest income</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>162456900</v>
       </c>
     </row>
   </sheetData>
@@ -20640,6 +23111,9 @@
           <t>(Catatan dan ) payable (Notes and )</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>-5213870779</v>
+      </c>
       <c r="C37" s="24" t="n">
         <v>2746415909</v>
       </c>
@@ -20677,6 +23151,9 @@
           <t>Biaya administrasi bank Bank administration fee</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>-200114367</v>
+      </c>
       <c r="C41" s="24" t="n">
         <v>-10916105464</v>
       </c>
@@ -20697,6 +23174,9 @@
           <t>Bunga pinjaman (Catatan dan ) Loan interest (Notes and )</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>-7595385703</v>
+      </c>
       <c r="C43" s="24" t="n">
         <v>-12409133027</v>
       </c>
@@ -20707,6 +23187,9 @@
           <t>Bunga pinjaman bank Interest bank loans</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>-69885071889</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>-78709243724</v>
       </c>
@@ -20717,6 +23200,9 @@
           <t>Bunga obligasi Bond interest</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>-38015129549</v>
+      </c>
       <c r="C45" s="24" t="n">
         <v>-189490717335</v>
       </c>
@@ -20810,6 +23296,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
@@ -21282,6 +23769,9 @@
           <t>Jumlah rata-rata saham tertimbang Weighted average number of shares</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>2321628564</v>
+      </c>
       <c r="C53" s="24" t="n">
         <v>3676392393</v>
       </c>
@@ -21307,6 +23797,7 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
@@ -21329,7 +23820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -21531,6 +24022,9 @@
           <t>PT Investasi Sukses Bersama PT Investasi Sukses Bersama</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>29898527954</v>
+      </c>
       <c r="C27" s="24" t="n">
         <v>346823968729</v>
       </c>
@@ -21541,6 +24035,9 @@
           <t>PT LHT Internasional PT LHT Internasional</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>9479046975</v>
+      </c>
       <c r="C28" s="24" t="n">
         <v>10216405360</v>
       </c>
@@ -21754,11 +24251,49 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 32 / Note: In 2024, this item was numbered Note 32</t>
         </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 32) / Note: Rows added from 2024 Annual Report (Note 32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Saldo awal - / Beginning balance</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>120262110434</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Pembayaran tahun berjalan - / Additional current year</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-120400198799</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Pajak atas penghasilan bunga - / Tax of interest income</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-24368535</v>
       </c>
     </row>
   </sheetData>
@@ -22891,6 +25426,9 @@
           <t>P endapatan neto . . Net revenues</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>316508228497</v>
+      </c>
       <c r="C40" s="24" t="n">
         <v>45378468775</v>
       </c>
@@ -22901,6 +25439,9 @@
           <t>Beban pokok pendapatan Costs of revenues</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>-166315532869</v>
+      </c>
       <c r="C41" s="24" t="n">
         <v>-294222040279</v>
       </c>
@@ -22911,6 +25452,9 @@
           <t>Laba bruto Gross profit</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>150192695628</v>
+      </c>
       <c r="C42" s="24" t="n">
         <v>151156428496</v>
       </c>
@@ -22921,6 +25465,9 @@
           <t>Beban usaha - neto Operating expenses - net</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>-29113844322</v>
+      </c>
       <c r="C43" s="24" t="n">
         <v>-14890103309</v>
       </c>
@@ -22931,6 +25478,9 @@
           <t>L aba usaha Operating profit</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>121078851306</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>136266325187</v>
       </c>
@@ -22948,6 +25498,9 @@
           <t>Aset segmen Segment assets</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>676271356533</v>
+      </c>
       <c r="C46" s="24" t="n">
         <v>1485960969772</v>
       </c>
@@ -22965,6 +25518,9 @@
           <t>Liabilitas segmen Segment liabilities</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>1360778694547</v>
+      </c>
       <c r="C48" s="24" t="n">
         <v>628385978817</v>
       </c>
@@ -22989,6 +25545,9 @@
           <t>Penyusutan Depreciations</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>-66898859984</v>
+      </c>
       <c r="C51" s="24" t="n">
         <v>-81526195149</v>
       </c>
@@ -23098,6 +25657,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
@@ -23120,7 +25680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -23270,6 +25830,9 @@
           <t>Amortisasi kerugian hari ke- untuk utang Amortization of day gain on payable</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>-47860049405</v>
+      </c>
       <c r="C20" s="24" t="n">
         <v>10284153005</v>
       </c>
@@ -23280,6 +25843,9 @@
           <t>Beban bunga kontraktual - neto Contractual interest expenses - net</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>7595385703</v>
+      </c>
       <c r="C21" s="24" t="n">
         <v>12017250000</v>
       </c>
@@ -23290,6 +25856,9 @@
           <t>Pajak penghasilan atas bunga Income tax on interest</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>-1139307855</v>
+      </c>
       <c r="C22" s="24" t="n">
         <v>-1802587500</v>
       </c>
@@ -23354,6 +25923,9 @@
           <t>Penambahan dari beban bunga Addition from interest expense</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>5903870779</v>
+      </c>
       <c r="C29" s="24" t="n">
         <v>3759547002</v>
       </c>
@@ -23371,6 +25943,9 @@
           <t>Penambahan dari beban bunga Addition from interest expense</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>14085074934</v>
+      </c>
       <c r="C31" s="24" t="n">
         <v>78717993754</v>
       </c>
@@ -23405,6 +25980,9 @@
           <t>Uang muka Advances</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>88384436054</v>
+      </c>
       <c r="C35" s="24" t="n">
         <v>286072400000</v>
       </c>
@@ -23415,6 +25993,9 @@
           <t>Pinjaman - Loans</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>33822690298</v>
+      </c>
       <c r="C36" s="24" t="n">
         <v>167781078247</v>
       </c>
@@ -23425,6 +26006,9 @@
           <t>Liabilitas sewa - Lease liabilities</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>2395482771</v>
+      </c>
       <c r="C37" s="24" t="n">
         <v>2395482771</v>
       </c>
@@ -23477,6 +26061,9 @@
           <t>konsumen - payables</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>39050233</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>1112682972</v>
       </c>
@@ -23487,6 +26074,9 @@
           <t>Utang bank - Bank loans</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>336846592826</v>
+      </c>
       <c r="C45" s="24" t="n">
         <v>375305504520</v>
       </c>
@@ -23497,6 +26087,9 @@
           <t>Liabilitas sewa Lease liabilities</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>226143265528</v>
+      </c>
       <c r="C46" s="24" t="n">
         <v>184251124095</v>
       </c>
@@ -23524,6 +26117,9 @@
           <t>panjang long terim</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>319375000000</v>
+      </c>
       <c r="C49" s="24" t="n">
         <v>301212468808</v>
       </c>
@@ -23534,6 +26130,9 @@
           <t>Utang pihak berelasi Due to a related party</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>10358361195</v>
+      </c>
       <c r="C50" s="24" t="n">
         <v>39377574929</v>
       </c>
@@ -23544,6 +26143,9 @@
           <t>Utang obligasi Bond payable</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>600000000000</v>
+      </c>
       <c r="C51" s="24" t="n">
         <v>614085074934</v>
       </c>
@@ -23656,11 +26258,29 @@
         <v>600000000000</v>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 36 / Note: In 2024, this item was numbered Note 36</t>
         </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 36) / Note: Rows added from 2024 Annual Report (Note 36)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pendapatan bunga kontraktual - / Contractual interest income</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>162456900</v>
       </c>
     </row>
   </sheetData>
@@ -23995,6 +26615,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
@@ -24017,7 +26638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -24334,11 +26955,29 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
           <t>Catatan: Pada tahun 2024, item ini bernomor Catatan 38 / Note: In 2024, this item was numbered Note 38</t>
         </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 38) / Note: Rows added from 2024 Annual Report (Note 38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>invoice yang di biayai sebesar Rp / and the value that can be</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>8679000000</v>
       </c>
     </row>
   </sheetData>
@@ -24735,7 +27374,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UMUM</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -24752,7 +27391,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INFORMASI KEBIJAKAN AKUNTANSI MATERIAL</t>
+          <t>MATERIAL ACCOUNTING POLICY INFORMATION</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -24769,7 +27408,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESTIMASI DAN PERTIMBANGAN AKUNTANSI</t>
+          <t>SIGNIFICANT ACCOUNTING ESTIMATES AND JUDGMENTS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -24786,7 +27425,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KAS DAN SETARA KAS</t>
+          <t>CASH AND CASH EQUIVALENTS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -24803,7 +27442,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PIUTANG USAHA</t>
+          <t>TRADE RECEIVABLES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -24833,7 +27472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BEBAN DIBAYAR DI MUKA DAN ASET LANCAR LAINNYA</t>
+          <t>PREPAID EXPENSES AND OTHER CURRENT ASSETS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -24850,7 +27489,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UANG MUKA</t>
+          <t>ADVANCES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -24880,7 +27519,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASET TETAP</t>
+          <t>FIXED ASSETS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -24897,7 +27536,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASET TAKBERWUJUD</t>
+          <t>INTANGIBLE ASSETS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -24927,7 +27566,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UTANG USAHA</t>
+          <t>TRADE PAYABLES</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -24944,7 +27583,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UTANG LAIN-LAIN</t>
+          <t>OTHER PAYABLES</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -24961,7 +27600,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BEBAN AKRUAL</t>
+          <t>ACCRUED EXPENSES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -24978,7 +27617,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UANG MUKA PENJUALAN</t>
+          <t>ADVANCES FROM CUSTOMERS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -24995,7 +27634,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LIABILITAS SEWA</t>
+          <t>LEASE LIABILITIES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -25025,7 +27664,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PERPAJAKAN</t>
+          <t>TAXATION</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -25042,7 +27681,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTANG PEMBIAYAAN KONSUMEN</t>
+          <t>CONSUMER FINANCING PAYABLES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -25059,7 +27698,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTANG BANK JANGKA PANJANG</t>
+          <t>LONG-TERM BANK LOANS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -25076,7 +27715,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTANG OBLIGASI</t>
+          <t>BONDS PAYABLE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -25093,7 +27732,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PINJAMAN</t>
+          <t>LOANS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -25110,7 +27749,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UTANG PIHAK BERELASI</t>
+          <t>DUE TO A RELATED PARTY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25140,7 +27779,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LIABILITAS IMBALAN KERJA</t>
+          <t>EMPLOYEE BENEFITS LIABILITY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -25157,7 +27796,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MODAL SAHAM DAN UANG MUKA SETORAN MODAL</t>
+          <t>SHARE CAPITAL</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -25174,7 +27813,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TAMBAHAN MODAL DISETOR</t>
+          <t>ADDITIONAL PAID-IN CAPITAL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -25191,7 +27830,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KEPENTINGAN NONPENGENDALI</t>
+          <t>NON-CONTROLLING INTEREST</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -25208,7 +27847,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PENDAPATAN USAHA - NETO</t>
+          <t>REVENUES - NET</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -25225,7 +27864,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BEBAN POKOK PENDAPATAN</t>
+          <t>COSTS OF REVENUES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -25242,7 +27881,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BEBAN OPERASIONAL</t>
+          <t>OPERATING EXPENSES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25259,7 +27898,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PENGHASILAN (BEBAN) LAIN-LAIN</t>
+          <t>OTHER INCOMES (EXPENSES)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -25276,7 +27915,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PENGHASILAN KEUANGAN</t>
+          <t>FINANCE INCOME</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25293,7 +27932,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BEBAN KEUANGAN</t>
+          <t>FINANCE EXPENSES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -25310,7 +27949,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LABA NETO PER SAHAM</t>
+          <t>EARNINGS PER SHARE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -25327,7 +27966,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INFORMASI PIHAK BERELASI</t>
+          <t>RELATED PARTIES INFORMATION</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -25344,7 +27983,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>INSTRUMEN KEUANGAN</t>
+          <t>FINANCIAL INSTRUMENTS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -25361,7 +28000,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KEBIJAKAN DAN TUJUAN MANAJEMEN RISIKO KEUANGAN</t>
+          <t>FINANCIAL RISK MANAGEMENT OBJECTIVES AND POLICIES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -25378,7 +28017,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>INFORMASI SEGMEN</t>
+          <t>SEGMENT INFORMATION</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -25395,7 +28034,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>INFORMASI TAMBAHAN ARUS KAS</t>
+          <t>SUPPLEMENTARY CASH FLOWS INFORMATION</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -25412,7 +28051,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IKATAN DAN KONTINJENSI</t>
+          <t>SIGNIFICANT AGREEMENTS, COMMITMENTS AND CONTINGENCIES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -25429,7 +28068,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PERISTIWA SETELAH PERIODE PELAPORAN</t>
+          <t>EVENTS AFTER REPORTING PERIOD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -25446,7 +28085,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PENERBITAN AMENDEMEN DAN PENYESUAIAN</t>
+          <t>ISSUANCE OF AMENDMENTS AND ADJUSTMENTS TO ACCOUNTING STANDARDS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -26968,7 +29607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -27163,6 +29802,9 @@
           <t>PT Bank Central Asia Tbk PT Bank Central Asia Tbk</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>775681807</v>
+      </c>
       <c r="C23" s="24" t="n">
         <v>97510373394</v>
       </c>
@@ -27180,6 +29822,9 @@
           <t>(Persero) Tbk (Persero) Tbk</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>19203097</v>
+      </c>
       <c r="C25" s="24" t="n">
         <v>89571850342</v>
       </c>
@@ -27223,6 +29868,9 @@
           <t>(Persero) Tbk (Persero) Tbk</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>5341082</v>
+      </c>
       <c r="C29" s="24" t="n">
         <v>68472517</v>
       </c>
@@ -27259,6 +29907,9 @@
           <t>PT Bank Mandiri (Persero) Tbk PT Bank Mandiri (Persero) Tbk</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>6518928</v>
+      </c>
       <c r="C32" s="24" t="n">
         <v>17138487</v>
       </c>
@@ -27295,6 +29946,9 @@
           <t>PT Bank IBK Indonesia Tbk PT Bank IBK Indonesia Tbk</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>2921715</v>
+      </c>
       <c r="C35" s="24" t="n">
         <v>2796923</v>
       </c>
@@ -27305,6 +29959,9 @@
           <t>PT Bank Amar Indonesia Tbk - PT Bank Amar Indonesia Tbk</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>10109671182</v>
+      </c>
       <c r="C36" s="24" t="n">
         <v>2695000</v>
       </c>
@@ -27375,6 +30032,9 @@
           <t>PT Bank Shinhan Indonesia - PT Bank Shinhan Indonesia</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>3132402761</v>
+      </c>
       <c r="C43" s="24" t="n">
         <v>500000000000</v>
       </c>
@@ -27385,6 +30045,9 @@
           <t>PT Bank Hibank Indonesia - PT Bank Hibank Indonesia</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>459524571</v>
+      </c>
       <c r="C44" s="24" t="n">
         <v>52615601854</v>
       </c>
@@ -27395,6 +30058,9 @@
           <t>PT Bank J Trust Indonesia - PT Bank J Trust Indonesia</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>9748805</v>
+      </c>
       <c r="C45" s="24" t="n">
         <v>22580485276</v>
       </c>
@@ -27485,6 +30151,23 @@
         <is>
           <t>PT Solusi Sinergi Digital Tbk Laporan Tahunan dan Laporan Keberlanjutan Annual Report and Sustainability Report surge.co.id surge.co.id PT Solusi Sinergi Digital Tbk Laporan Tahunan dan Laporan Keberlanjutan Annual Report and Sustainability Report</t>
         </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>Catatan: Baris berikut hanya muncul di Laporan Tahunan 2024 (Catatan 4) / Note: Rows added from 2024 Annual Report (Note 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PT Bank OCBC NISP Tbk - / PT Bank OCBC NISP Tbk</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>35000000000</v>
       </c>
     </row>
   </sheetData>
